--- a/forms/trg/Formulir_TRG_corpaudit.xlsx
+++ b/forms/trg/Formulir_TRG_corpaudit.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -686,126 +686,114 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>ID peneliti (SINTA/Scopus/ORCID) banyak yang kosong.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
           <t>Belum ada artikel tercatat di situs. Mohon cantumkan riset terbaik di lembar TRG &amp; Riset.</t>
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Contoh pengisian (hanya ilustrasi, jangan disalin)</t>
+        </is>
+      </c>
+    </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Contoh pengisian (hanya ilustrasi, jangan disalin)</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Nama</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Dr. Contoh Nama, S.Pi., M.Si.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Nama</t>
+          <t>Keahlian utama 1-3 (pilih)</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Dr. Contoh Nama, S.Pi., M.Si.</t>
+          <t>Perikanan &amp; akuakultur; Ekosistem pesisir &amp; laut</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Keahlian utama 1-3 (pilih)</t>
+          <t>Kata kunci keahlian</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Perikanan &amp; akuakultur; Ekosistem pesisir &amp; laut</t>
+          <t>budidaya udang, kualitas air, bioflok</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Kata kunci keahlian</t>
+          <t>SINTA ID</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>budidaya udang, kualitas air, bioflok</t>
+          <t>6012345</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>SINTA ID</t>
+          <t>ORCID</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>6012345</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>ORCID</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
           <t>0000-0002-1234-5678</t>
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Kemajuan pengisian (otomatis)</t>
+        </is>
+      </c>
+    </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Kemajuan pengisian (otomatis)</t>
-        </is>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Anggota tercantum</t>
+        </is>
+      </c>
+      <c r="B24" s="7">
+        <f>COUNTA(Anggota!B5:B24)</f>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Anggota tercantum</t>
+          <t>Anggota dengan keahlian terpilih</t>
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!B5:B23)</f>
+        <f>COUNTA(Anggota!F5:F24)</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Anggota dengan keahlian terpilih</t>
-        </is>
-      </c>
-      <c r="B26" s="7">
-        <f>COUNTA(Anggota!F5:F23)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
           <t>Persentase anggota berkeahlian</t>
         </is>
       </c>
-      <c r="B27" s="8">
-        <f>IF(B25=0,0,B26/B25)</f>
+      <c r="B26" s="8">
+        <f>IF(B24=0,0,B25/B24)</f>
         <v/>
       </c>
     </row>
@@ -820,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -925,37 +913,37 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Kartini, SE., M.Si., Ak., CA.</t>
+          <t>Prof. Dr. Arifuddin, SE., M.Si., Ak., CA.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Department of Accounting, Faculty of Economics and Business Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Accounting Public</t>
+          <t>Auditing</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-2938-4613%20View%20this%20author’s%20ORCID%20profile</t>
+        </is>
+      </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>6033555</t>
+          <t>6029842</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57202739259</t>
+          <t>56971486100</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -970,12 +958,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Fadly Achmad Arifuddin Mannan, S.E., M.Si., Ak</t>
+          <t>Prof. Dr. Kartini, SE., M.Si., Ak., CA.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -985,7 +973,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Auditing</t>
+          <t>Accounting Public</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -993,8 +981,16 @@
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="12" t="n"/>
-      <c r="K6" s="12" t="n"/>
-      <c r="L6" s="12" t="n"/>
+      <c r="K6" s="11" t="inlineStr">
+        <is>
+          <t>6033555</t>
+        </is>
+      </c>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>57202739259</t>
+        </is>
+      </c>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1007,12 +1003,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Rizky Utami, SE., M.Acc., Fin</t>
+          <t>Fadly Achmad Arifuddin Mannan, S.E., M.Si., Ak</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1022,7 +1018,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Financial Accounting, Digital Finance, Environmental Accounting, Shariah Accounting</t>
+          <t>Auditing</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1031,11 +1027,7 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="12" t="n"/>
       <c r="K7" s="12" t="n"/>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>57213186692</t>
-        </is>
-      </c>
+      <c r="L7" s="12" t="n"/>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1048,22 +1040,22 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Nguyen Thi Kim Tuyen</t>
+          <t>Rizky Utami, SE., M.Acc., Fin</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Ton Duc Thang University</t>
+          <t>Department of Accounting, Faculty of Economics and Business Hasanuddin University</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Financial Accounting, Digital Finance, Environmental Accounting, Shariah Accounting</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1072,7 +1064,11 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="12" t="n"/>
       <c r="K8" s="12" t="n"/>
-      <c r="L8" s="12" t="n"/>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>57213186692</t>
+        </is>
+      </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1085,17 +1081,17 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Anas Mosleh Al Mhasnah</t>
+          <t>Nguyen Thi Kim Tuyen</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Mutah university, Jordan</t>
+          <t>Ton Duc Thang University</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -1122,22 +1118,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Fauzan Garantjang, S.E., M.Ak., Ak., ACPA</t>
+          <t>Anas Mosleh Al Mhasnah</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Department Acoounting Faculty of Economics and Business Hasanuddin University</t>
+          <t>Mutah university, Jordan</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Auditing, Public Accounting</t>
+          <t>Accounting</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1159,16 +1155,24 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Ferry Christian</t>
+          <t>Muhammad Fauzan Garantjang, S.E., M.Ak., Ak., ACPA</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="11" t="n"/>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Department Acoounting Faculty of Economics and Business Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Auditing, Public Accounting</t>
+        </is>
+      </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
@@ -1186,10 +1190,22 @@
       <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Ferry Christian</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D12" s="12" t="n"/>
-      <c r="E12" s="11" t="n"/>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Welcome to the official website of the Corporate Auditing Research Group . Our research group members also have a wealth of advisory and consultative experience and a demonstrated commitment to providing objective, technical, and evidence-driven advice.</t>
+        </is>
+      </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
@@ -1197,7 +1213,11 @@
       <c r="J12" s="12" t="n"/>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="12" t="n"/>
-      <c r="M12" s="12" t="n"/>
+      <c r="M12" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1386,15 +1406,32 @@
       <c r="L23" s="12" t="n"/>
       <c r="M23" s="12" t="n"/>
     </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="12" t="n"/>
+      <c r="G24" s="12" t="n"/>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="12" t="n"/>
+      <c r="J24" s="12" t="n"/>
+      <c r="K24" s="12" t="n"/>
+      <c r="L24" s="12" t="n"/>
+      <c r="M24" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
